--- a/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
+++ b/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PortableProgram\Gvrer\gvrer-2023.2.190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28B31C49-7CC8-41A7-B614-ACE4BA9E7594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C593EA80-42AB-4A0B-9964-1DD62BEEB260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{9E302954-96F8-4470-AEA4-F00A64E90A02}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>login</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>i</t>
+  </si>
+  <si>
+    <t>encontrar("u2@g", ***)</t>
+  </si>
+  <si>
+    <t>u3@g</t>
   </si>
 </sst>
 </file>
@@ -442,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{419C1C56-0FFF-44AB-A62D-EE12D9275A08}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -475,7 +481,9 @@
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
@@ -493,19 +501,27 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{7A4624F4-CB4E-4437-8BC5-A85F9D2225B5}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{4684B2C9-AA49-428E-A8FA-2BC481CA1F71}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{D09ADE50-2E59-4934-BAAC-97DF6DC760D8}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
+++ b/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PortableProgram\Gvrer\gvrer-2023.2.190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C593EA80-42AB-4A0B-9964-1DD62BEEB260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF69F92-8BB3-4A97-8EF8-59262E916A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{9E302954-96F8-4470-AEA4-F00A64E90A02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" firstSheet="3" activeTab="3" xr2:uid="{9E302954-96F8-4470-AEA4-F00A64E90A02}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="TIPOCONTATO" sheetId="2" r:id="rId2"/>
+    <sheet name="CATEGORIADAEMPRESA" sheetId="3" r:id="rId3"/>
+    <sheet name="PESSOA" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>login</t>
   </si>
@@ -61,6 +64,66 @@
   </si>
   <si>
     <t>u3@g</t>
+  </si>
+  <si>
+    <t>TIPOCONTATOID</t>
+  </si>
+  <si>
+    <t>NOMETIPOCOTATO</t>
+  </si>
+  <si>
+    <t>CELULAR</t>
+  </si>
+  <si>
+    <t>WPP</t>
+  </si>
+  <si>
+    <t>COMERCIAL</t>
+  </si>
+  <si>
+    <t>E-MAL</t>
+  </si>
+  <si>
+    <t>TELEFONE FIXO</t>
+  </si>
+  <si>
+    <t>CATEGORIADAEMPRESAID</t>
+  </si>
+  <si>
+    <t>NOMECATEGORIADAEMPRESA</t>
+  </si>
+  <si>
+    <t>ATACADO</t>
+  </si>
+  <si>
+    <t>VAREJO</t>
+  </si>
+  <si>
+    <t>ATACADO E VAREJO</t>
+  </si>
+  <si>
+    <t>JURIDICAID</t>
+  </si>
+  <si>
+    <t>RAZAOSOCIAL</t>
+  </si>
+  <si>
+    <t>ATACK</t>
+  </si>
+  <si>
+    <t>NOVA ERA</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>ASSAÍ</t>
+  </si>
+  <si>
+    <t>BARATÃO DA CARNE</t>
+  </si>
+  <si>
+    <t>SUPERM. VITÓRIA</t>
   </si>
 </sst>
 </file>
@@ -524,4 +587,209 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DBD733-35D6-4D79-8985-05F7A66C796B}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB89D43C-1063-47B0-B5B6-A7A86EDFF9D3}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC6EE1F-16A7-4D90-8063-CC65E1BAE27B}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
+++ b/src/main/resources/templates/gvrer-2023.2.190/db.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PortableProgram\Gvrer\gvrer-2023.2.190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF69F92-8BB3-4A97-8EF8-59262E916A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86ECA61D-DB7D-43C8-9FC2-7DDD1AD70792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" firstSheet="3" activeTab="3" xr2:uid="{9E302954-96F8-4470-AEA4-F00A64E90A02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="5" xr2:uid="{9E302954-96F8-4470-AEA4-F00A64E90A02}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="TIPOCONTATO" sheetId="2" r:id="rId2"/>
-    <sheet name="CATEGORIADAEMPRESA" sheetId="3" r:id="rId3"/>
-    <sheet name="PESSOA" sheetId="4" r:id="rId4"/>
+    <sheet name="ESTADO" sheetId="5" r:id="rId2"/>
+    <sheet name="PAIS" sheetId="6" r:id="rId3"/>
+    <sheet name="TIPOCONTATO" sheetId="2" r:id="rId4"/>
+    <sheet name="CATEGORIADAEMPRESA" sheetId="3" r:id="rId5"/>
+    <sheet name="PESSOA" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>login</t>
   </si>
@@ -124,6 +126,48 @@
   </si>
   <si>
     <t>SUPERM. VITÓRIA</t>
+  </si>
+  <si>
+    <t>ESTADOID</t>
+  </si>
+  <si>
+    <t>NOMEESTADO</t>
+  </si>
+  <si>
+    <t>PAISID</t>
+  </si>
+  <si>
+    <t>AMAZONAS</t>
+  </si>
+  <si>
+    <t>NOMEPAIS</t>
+  </si>
+  <si>
+    <t>BRASIL</t>
+  </si>
+  <si>
+    <t>ACRE</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>ENDERECOID</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>NOMEFANTASIA</t>
+  </si>
+  <si>
+    <t>ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>DB CIDADE NOVA</t>
+  </si>
+  <si>
+    <t>DB CENTRO</t>
   </si>
 </sst>
 </file>
@@ -590,6 +634,94 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DFEB8C-660E-412D-B5CB-D8A29F806C1E}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9310235A-F3EC-4693-9D6C-850258B8CB75}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DBD733-35D6-4D79-8985-05F7A66C796B}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -656,7 +788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB89D43C-1063-47B0-B5B6-A7A86EDFF9D3}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -702,91 +834,131 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC6EE1F-16A7-4D90-8063-CC65E1BAE27B}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
       <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2">
-        <v>2</v>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
